--- a/output/pdf_financials_xlsx/SNV.xlsx
+++ b/output/pdf_financials_xlsx/SNV.xlsx
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-6.908384</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-6.908384</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-6.908384</v>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-58.44344</v>
+        <v>58.44344</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-91.79276</v>
+        <v>91.79276</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>115.139733</v>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-7.084358</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-7.084358</v>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-6.908384</v>
@@ -7803,19 +7803,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.189534</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-4.996195</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.264707</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.372586</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>13.624134</v>
+        <v>13.649217</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.890505</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.620685</v>
       </c>
     </row>
     <row r="119">
@@ -26406,7 +26406,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -40118,7 +40122,11 @@
           <t>Purchases/reimbursements of exploration and evaluation expenditures 14</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -41502,7 +41510,11 @@
           <t>Purchases of exploration and evaluation expenditures 14</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -42791,7 +42803,11 @@
           <t>Purchases of exploration and evaluation expenditures 15</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -45094,7 +45110,11 @@
           <t>Purchases of exploration and evaluation expenditures 13</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -75425,10 +75445,10 @@
         </is>
       </c>
       <c r="E666" s="5" t="n">
-        <v>5.844344</v>
+        <v>-5.844344</v>
       </c>
       <c r="F666" s="5" t="n">
-        <v>4.589638</v>
+        <v>-4.589638</v>
       </c>
       <c r="G666" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SNV.xlsx
+++ b/output/pdf_financials_xlsx/SNV.xlsx
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.017658</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007159999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.175974</v>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.844344</v>
+        <v>-5.862002</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.589638</v>
+        <v>-4.590354</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-7.084358</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.844344</v>
+        <v>-5.862002</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.589638</v>
+        <v>-4.590354</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-7.084358</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.491737</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.025617</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.025617</v>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.491737</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.025617</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.025617</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.577442</v>
+        <v>0.085705</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015368</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023051</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015368</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023051</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -20992,7 +20992,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -48924,7 +48924,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E401" s="5" t="n">
         <v>-0.015368</v>
       </c>
@@ -50540,7 +50544,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -58629,7 +58633,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -74130,7 +74134,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E653" s="5" t="n">

--- a/output/pdf_financials_xlsx/SNV.xlsx
+++ b/output/pdf_financials_xlsx/SNV.xlsx
@@ -2099,40 +2099,40 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.104343</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.092075</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.07825500000000001</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.073313</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.050916</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.014317</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.016038</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.024878</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.019792</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.018713</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.019821</v>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.172807</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2159,40 +2159,40 @@
         <v>-4.590354</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.084358</v>
+        <v>-6.980015</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-9.206687000000001</v>
+        <v>-9.114611999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.240168</v>
+        <v>-4.161913</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.177506</v>
+        <v>-5.104193</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-16.172846</v>
+        <v>-16.12193</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.233058</v>
+        <v>-1.218741</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.570089</v>
+        <v>-7.554051</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.467051</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.365837</v>
+        <v>-1.340959</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.344196</v>
+        <v>-1.324404</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.629003</v>
+        <v>-2.61029</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.35461</v>
+        <v>-1.334789</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.481904</v>
+        <v>-4.309097</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-1.058229</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-1526.580855680181</v>
+        <v>-1467.721081368298</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>-3402.556187903926</v>
@@ -6759,46 +6759,46 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.104343</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.092075</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.07825500000000001</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.073313</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.050916</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.014317</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.016038</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.024878</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.019792</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.018713</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.019821</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.172807</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>0</v>
@@ -25555,7 +25555,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -28340,7 +28344,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -30253,7 +30261,11 @@
           <t>Depreciation of Property, Plant and Equipment 8</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -31243,7 +31255,11 @@
           <t>Depreciation of Property, Plant and Equipment 7</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -33126,7 +33142,11 @@
           <t>Depreciation of property Plant and Equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -35540,7 +35560,11 @@
           <t>Depreciation of property Plant and Equipment</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -37037,7 +37061,11 @@
           <t>Depreciation of property Plant and Equipment</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -37736,7 +37764,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -39045,7 +39077,11 @@
           <t>Depreciation of property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -43906,7 +43942,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -50740,7 +50780,11 @@
           <t>Depletion of property and equipment 7</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -58730,7 +58774,11 @@
           <t>Depreciation of property, plant, and equipment 7</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -63508,7 +63556,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -66423,7 +66475,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
@@ -66460,10 +66516,10 @@
         </is>
       </c>
       <c r="L576" s="5" t="n">
-        <v>-0.014317</v>
+        <v>0.014317</v>
       </c>
       <c r="M576" s="5" t="n">
-        <v>-0.016038</v>
+        <v>0.016038</v>
       </c>
       <c r="N576" t="inlineStr">
         <is>
@@ -67524,7 +67580,11 @@
           <t>Depreciation of property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
           <t>-</t>
@@ -67541,16 +67601,16 @@
         </is>
       </c>
       <c r="H587" s="5" t="n">
-        <v>-0.092075</v>
+        <v>0.092075</v>
       </c>
       <c r="I587" s="5" t="n">
-        <v>-0.07825500000000001</v>
+        <v>0.07825500000000001</v>
       </c>
       <c r="J587" s="5" t="n">
-        <v>-0.073313</v>
+        <v>0.073313</v>
       </c>
       <c r="K587" s="5" t="n">
-        <v>-0.050916</v>
+        <v>0.050916</v>
       </c>
       <c r="L587" t="inlineStr">
         <is>
@@ -70704,7 +70764,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
@@ -70716,10 +70780,10 @@
         </is>
       </c>
       <c r="G619" s="5" t="n">
-        <v>-0.104343</v>
+        <v>0.104343</v>
       </c>
       <c r="H619" s="5" t="n">
-        <v>-0.092075</v>
+        <v>0.092075</v>
       </c>
       <c r="I619" t="inlineStr">
         <is>
